--- a/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0005_ses-01_WMprob_pdf.xlsx
+++ b/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0005_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1174,7 +1175,7 @@
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.0024613566998129347</v>
       </c>
       <c r="B30" s="0">
         <v>0</v>
@@ -1592,7 +1593,7 @@
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>3.768337107413624</v>
+        <v>3.7683371074136241</v>
       </c>
       <c r="B41" s="0">
         <v>7.0175438596491553</v>
@@ -1657,7 +1658,7 @@
         <v>4.8936466008619446</v>
       </c>
       <c r="J42" s="0">
-        <v>5.373573794626421</v>
+        <v>5.3735737946264211</v>
       </c>
       <c r="K42" s="0">
         <v>11.211340206185557</v>
@@ -1736,7 +1737,7 @@
         <v>4.8030916451969041</v>
       </c>
       <c r="K44" s="0">
-        <v>8.6340206185566934</v>
+        <v>8.6340206185566935</v>
       </c>
       <c r="L44" s="0">
         <v>4.3386309209093978</v>
@@ -1777,7 +1778,7 @@
         <v>5.4123711340206135</v>
       </c>
       <c r="L45" s="0">
-        <v>4.0929306752091525</v>
+        <v>4.0929306752091526</v>
       </c>
     </row>
     <row r="46">
@@ -1829,7 +1830,7 @@
         <v>3.8067944052042431</v>
       </c>
       <c r="D47" s="0">
-        <v>3.0942706705455389</v>
+        <v>3.094270670545539</v>
       </c>
       <c r="E47" s="0">
         <v>3.6677705182135676</v>
@@ -1940,7 +1941,7 @@
         <v>0.96491228070175361</v>
       </c>
       <c r="C50" s="0">
-        <v>3.1309045257992087</v>
+        <v>3.1309045257992088</v>
       </c>
       <c r="D50" s="0">
         <v>3.1255259298439615</v>
@@ -1967,7 +1968,7 @@
         <v>0.5154639175257727</v>
       </c>
       <c r="L50" s="0">
-        <v>3.1956582589493951</v>
+        <v>3.1956582589493952</v>
       </c>
     </row>
     <row r="51">
@@ -2174,7 +2175,7 @@
         <v>2.2503786694876524</v>
       </c>
       <c r="E56" s="0">
-        <v>2.5865926787791977</v>
+        <v>2.5865926787791978</v>
       </c>
       <c r="F56" s="0">
         <v>2.0740093876214369</v>
@@ -2200,7 +2201,7 @@
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>2.3481342916215659</v>
+        <v>2.348134291621566</v>
       </c>
       <c r="B57" s="0">
         <v>1.5789473684210689</v>
@@ -2259,7 +2260,7 @@
         <v>1.991550995775496</v>
       </c>
       <c r="H58" s="0">
-        <v>1.7099358063966354</v>
+        <v>1.7099358063966355</v>
       </c>
       <c r="I58" s="0">
         <v>1.9264761375146453</v>
@@ -2303,7 +2304,7 @@
         <v>1.8768246906714845</v>
       </c>
       <c r="J59" s="0">
-        <v>1.7666543982333442</v>
+        <v>1.7666543982333443</v>
       </c>
       <c r="K59" s="0">
         <v>0</v>
@@ -2446,7 +2447,7 @@
         <v>1.6246406869701255</v>
       </c>
       <c r="G63" s="0">
-        <v>1.810500905250451</v>
+        <v>1.8105009052504511</v>
       </c>
       <c r="H63" s="0">
         <v>1.8917230017610618</v>
@@ -2537,7 +2538,7 @@
         <v>1.1597938144329887</v>
       </c>
       <c r="L65" s="0">
-        <v>1.349796286505146</v>
+        <v>1.3497962865051461</v>
       </c>
     </row>
     <row r="66">
@@ -2595,7 +2596,7 @@
         <v>1.683821116381752</v>
       </c>
       <c r="F67" s="0">
-        <v>1.2880689881017346</v>
+        <v>1.2880689881017347</v>
       </c>
       <c r="G67" s="0">
         <v>1.0863005431502706</v>
@@ -2642,7 +2643,7 @@
         <v>1.2781912174061227</v>
       </c>
       <c r="I68" s="0">
-        <v>1.0684991360648239</v>
+        <v>1.068499136064824</v>
       </c>
       <c r="J68" s="0">
         <v>1.3065881486934106</v>
@@ -2674,7 +2675,7 @@
         <v>1.2262125677691789</v>
       </c>
       <c r="G69" s="0">
-        <v>1.8105009052504712</v>
+        <v>1.8105009052504713</v>
       </c>
       <c r="H69" s="0">
         <v>1.1645742203033693</v>
@@ -2700,7 +2701,7 @@
         <v>0.26315789473684187</v>
       </c>
       <c r="C70" s="0">
-        <v>1.0626561330983137</v>
+        <v>1.0626561330983138</v>
       </c>
       <c r="D70" s="0">
         <v>0.82225374462048839</v>
@@ -2776,7 +2777,7 @@
         <v>0.17543859649122792</v>
       </c>
       <c r="C72" s="0">
-        <v>1.0017880013695319</v>
+        <v>1.001788001369532</v>
       </c>
       <c r="D72" s="0">
         <v>0.60827543096194026</v>
@@ -2960,7 +2961,7 @@
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.75809786354238395</v>
+        <v>0.75809786354238396</v>
       </c>
       <c r="B77" s="0">
         <v>0.70175438596491169</v>
@@ -2969,7 +2970,7 @@
         <v>0.71393246173550196</v>
       </c>
       <c r="D77" s="0">
-        <v>0.30053133940807319</v>
+        <v>0.3005313394080732</v>
       </c>
       <c r="E77" s="0">
         <v>0.78104955398430664</v>
@@ -3165,7 +3166,7 @@
         <v>0.43855723619440168</v>
       </c>
       <c r="F82" s="0">
-        <v>0.48211621729797099</v>
+        <v>0.482116217297971</v>
       </c>
       <c r="G82" s="0">
         <v>0.80466706900020935</v>
@@ -3177,7 +3178,7 @@
         <v>0.32571349129113952</v>
       </c>
       <c r="J82" s="0">
-        <v>0.55207949944792611</v>
+        <v>0.55207949944792612</v>
       </c>
       <c r="K82" s="0">
         <v>0</v>
@@ -3232,7 +3233,7 @@
         <v>0.61403508771929771</v>
       </c>
       <c r="C84" s="0">
-        <v>0.27517467885720059</v>
+        <v>0.2751746788572006</v>
       </c>
       <c r="D84" s="0">
         <v>0.22599956723487105</v>
@@ -3358,7 +3359,7 @@
         <v>0.34202961830950013</v>
       </c>
       <c r="G87" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H87" s="0">
         <v>0.22723399420553292</v>
@@ -3428,7 +3429,7 @@
         <v>0.084148775034260492</v>
       </c>
       <c r="E89" s="0">
-        <v>0.15692592261105628</v>
+        <v>0.15692592261105629</v>
       </c>
       <c r="F89" s="0">
         <v>0.22377469708547082</v>
@@ -3563,7 +3564,7 @@
         <v>0.38659793814432958</v>
       </c>
       <c r="L92" s="0">
-        <v>0.1570615494666126</v>
+        <v>0.15706154946661261</v>
       </c>
     </row>
     <row r="93">
@@ -3703,7 +3704,7 @@
         <v>0.080466706900020044</v>
       </c>
       <c r="H96" s="0">
-        <v>0.090893597682213167</v>
+        <v>0.090893597682213168</v>
       </c>
       <c r="I96" s="0">
         <v>0.029790868105896578</v>
@@ -3788,7 +3789,7 @@
         <v>0.055207949944792008</v>
       </c>
       <c r="K98" s="0">
-        <v>1.9329896907216479</v>
+        <v>1.932989690721648</v>
       </c>
       <c r="L98" s="0">
         <v>0.012440518769632683</v>
@@ -3796,7 +3797,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.024613566998129346</v>
+        <v>0.024613566998129347</v>
       </c>
       <c r="B99" s="0">
         <v>0.26315789473684187</v>
